--- a/naver-place-crawler/results_health/금정구_PT.xlsx
+++ b/naver-place-crawler/results_health/금정구_PT.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>핏핏바디트레이닝 PT센터 금정본점</t>
+          <t>범어휘트니스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fitfitness@naver.com</t>
+          <t>jfitness-@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>051-512-5868</t>
+          <t>0507-1406-1969</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금샘로 387-1 2층</t>
+          <t>부산광역시 금정구 중앙대로 2096 1층 범어휘트니스 by j.f.c</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitfitness</t>
+          <t>https://blog.naver.com/jfitness-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>214</v>
+        <v>387</v>
       </c>
       <c r="Q2" t="n">
-        <v>313</v>
+        <v>107</v>
       </c>
       <c r="R2" t="n">
-        <v>527</v>
+        <v>494</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +636,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>37302400</t>
+          <t>1512578499</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37302400</t>
+          <t>https://m.place.naver.com/place/1512578499</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>무지개휘트니스 남산점PT&amp;필라테스&amp;요가&amp;줌바</t>
+          <t>핏핏바디트레이닝 PT센터 금정본점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rainbow4441@naver.com</t>
+          <t>fitfitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1442-4445</t>
+          <t>051-512-5868</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 700 남산빌딩 4층 무지개휘트니스</t>
+          <t>부산광역시 금정구 금샘로 387-1 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/rainbow4441</t>
+          <t>https://blog.naver.com/fitfitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>886</v>
+        <v>214</v>
       </c>
       <c r="Q3" t="n">
-        <v>876</v>
+        <v>313</v>
       </c>
       <c r="R3" t="n">
-        <v>1762</v>
+        <v>527</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>381975477</t>
+          <t>37302400</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/381975477</t>
+          <t>https://m.place.naver.com/place/37302400</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>천지연피트니스</t>
+          <t>맨하탄 필라테스&amp;헬스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cjy98501@naver.com</t>
+          <t>manhattan80@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1363-9851</t>
+          <t>0507-1383-9711</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부곡온천천로 126 삼승렉스풀 상가2층</t>
+          <t>부산광역시 금정구 중앙대로1841번길 23 현대타운 8층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cjy98501</t>
+          <t>https://blog.naver.com/manhattan80</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>66</v>
+        <v>463</v>
       </c>
       <c r="Q4" t="n">
-        <v>31</v>
+        <v>201</v>
       </c>
       <c r="R4" t="n">
-        <v>97</v>
+        <v>664</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,56 +824,56 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1458862347</t>
+          <t>11663411</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1458862347</t>
+          <t>https://m.place.naver.com/place/11663411</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>핏머슬짐 남산동pt 남산동재활운동</t>
+          <t>오성피트니스 부산대점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fit_muscle__gym@naver.com</t>
+          <t>hakunashop@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1347-4634</t>
+          <t>0507-1361-4120</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 청룡로 43 도순빌딩 2층</t>
+          <t>부산광역시 금정구 부산대학로 49 8층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_fit_muscle__gym</t>
+          <t>http://osungfit.com/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>18</v>
+        <v>619</v>
       </c>
       <c r="Q5" t="n">
-        <v>15</v>
+        <v>252</v>
       </c>
       <c r="R5" t="n">
-        <v>33</v>
+        <v>871</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,61 +918,61 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1073265057</t>
+          <t>1229455757</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1073265057</t>
+          <t>https://m.place.naver.com/place/1229455757</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>에이치코어운동센터</t>
+          <t>대기구필라테스청담 서동점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>thth806@naver.com</t>
+          <t>cjdeka0502@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1325-5168</t>
+          <t>0507-1387-0018</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 514 3층</t>
+          <t>부산광역시 금정구 서동로 168 9층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://pf.kakao.com/_txhfbG</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -988,22 +988,22 @@
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>484</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>422</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>906</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1012,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1437613013</t>
+          <t>1651565560</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1437613013</t>
+          <t>https://m.place.naver.com/place/1651565560</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NSgym</t>
+          <t>이룸핏 헬스&amp;PT 온천장점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rocksr1945@naver.com</t>
+          <t>erumfit0415@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1422-2918</t>
+          <t>0507-1392-7832</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로 2049 3, 4층</t>
+          <t>부산광역시 금정구 식물원로 25 3층 이룸핏 온천장점</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/nsgym7/</t>
+          <t>https://blog.naver.com/erumfit0415</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>104</v>
+        <v>185</v>
       </c>
       <c r="Q7" t="n">
-        <v>82</v>
+        <v>532</v>
       </c>
       <c r="R7" t="n">
-        <v>186</v>
+        <v>717</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,17 +1106,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1220858968</t>
+          <t>1124866804</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1220858968</t>
+          <t>https://m.place.naver.com/place/1124866804</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하와이피티</t>
+          <t>비너스짐</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>whwlgns83@naver.com</t>
+          <t>iamjollykim@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1301-0781</t>
+          <t>0507-1464-6250</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1719번길 56 b1</t>
+          <t>부산광역시 금정구 부산대학로 31 3,4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/whwlgns83</t>
+          <t>https://www.instagram.com/venusgym.busan</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>208</v>
       </c>
       <c r="R8" t="n">
-        <v>27</v>
+        <v>408</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1200,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1475186578</t>
+          <t>1858723770</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1475186578</t>
+          <t>https://m.place.naver.com/place/1858723770</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>다이어트,비만</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>닥터핏24</t>
+          <t>웰니스점핑</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>drf24@naver.com</t>
+          <t>adam2400@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>051-710-8006</t>
+          <t>051-513-1588</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로 1829 12층 닥터핏24, 13층 닥터골프</t>
+          <t>부산광역시 금정구 금강로 494 구서골드 3상가 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://drfit24-golf.com/</t>
+          <t>https://blog.naver.com/adam2400</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>351</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>364</v>
+        <v>4</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1696181456</t>
+          <t>1219277187</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1696181456</t>
+          <t>https://m.place.naver.com/place/1219277187</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1316,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>아이라이크핏</t>
+          <t>핏핏바디트레이닝 PT센터 부산대점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hc0music@naver.com</t>
+          <t>fitfitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1349-7781</t>
+          <t>0507-1404-5838</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금정로 185 2층</t>
+          <t>부산광역시 금정구 금강로 209-1 3층 301호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hc0music</t>
+          <t>https://blog.naver.com/fitfitness</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1364,7 +1364,7 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="Q10" t="n">
-        <v>21</v>
+        <v>201</v>
       </c>
       <c r="R10" t="n">
-        <v>67</v>
+        <v>349</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1388,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1053373474</t>
+          <t>736873028</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1053373474</t>
+          <t>https://m.place.naver.com/place/736873028</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>시각디자인</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>현휘트니스</t>
+          <t>위너스피티</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hyeonfitness@naver.com</t>
+          <t>winnerspt@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1333-1203</t>
+          <t>051-904-7315</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로 1617-12 2층</t>
+          <t>부산광역시 금정구 중앙대로1959번길 8 3층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyeonfitness</t>
+          <t>https://blog.naver.com/winnerspt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1463,17 +1463,17 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>204</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>425</v>
+        <v>1</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1482,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1004485815</t>
+          <t>13466460</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1004485815</t>
+          <t>https://m.place.naver.com/place/13466460</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1504,25 +1504,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>레고핏 피트니스 구서점</t>
+          <t>반반피트니스 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>luvrover99@naver.com</t>
+          <t>b_b__fitness@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>051-532-9682</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1929번길 11 유림빌딩 2층</t>
+          <t>부산광역시 금정구 서동중심로 62 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/luvrover99</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1532,12 +1536,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1553,17 +1557,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>295</v>
+        <v>1122</v>
       </c>
       <c r="Q12" t="n">
-        <v>305</v>
+        <v>216</v>
       </c>
       <c r="R12" t="n">
-        <v>600</v>
+        <v>1338</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,47 +1576,51 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1940991515</t>
+          <t>1825995735</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1940991515</t>
+          <t>https://m.place.naver.com/place/1825995735</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>유도장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>부곡 김사부 유도관</t>
+          <t>핏핏바디트레이닝 PT센터 구서점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dusilyura@naver.com</t>
+          <t>fitfitness@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>051-512-5818</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부곡로 169</t>
+          <t>부산광역시 금정구 중앙대로1873번길 14 3층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ksb_judo/</t>
+          <t>https://blog.naver.com/fitfitness</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1627,7 +1635,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1647,13 +1655,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>212</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>193</v>
       </c>
       <c r="R13" t="n">
-        <v>10</v>
+        <v>405</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,17 +1670,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1783241619</t>
+          <t>38642628</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1783241619</t>
+          <t>https://m.place.naver.com/place/38642628</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1684,29 +1692,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>오성피트니스 부산대점</t>
+          <t>부산레포츠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>hakunashop@naver.com</t>
+          <t>songyum84@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1361-4120</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부산대학로 49 8층</t>
+          <t>부산광역시 금정구 금강로335번길 43</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>http://osungfit.com/</t>
+          <t>http://051-582-8787.okqr.co.kr</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1741,13 +1745,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>619</v>
+        <v>38</v>
       </c>
       <c r="Q14" t="n">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="R14" t="n">
-        <v>871</v>
+        <v>234</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,51 +1760,55 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1229455757</t>
+          <t>11781881</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1229455757</t>
+          <t>https://m.place.naver.com/place/11781881</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>짐핏 부산</t>
+          <t>메디앤컬필라테스 구서점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>da-_-in@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>medincurl_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>sample@sample.or.kr</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1333-0826</t>
+          <t>0507-1469-3741</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 수림로85번길 53 2층, 3층</t>
+          <t>부산광역시 금정구 중앙대로1841번길 35 7층 메디앤컬필라테스</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymfit.yh</t>
+          <t>http://www.medincurl.com/</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,7 +1818,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1826,7 +1834,7 @@
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1835,13 +1843,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>576</v>
       </c>
       <c r="Q15" t="n">
-        <v>11</v>
+        <v>257</v>
       </c>
       <c r="R15" t="n">
-        <v>15</v>
+        <v>833</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,17 +1858,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1005096569</t>
+          <t>532361433</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1005096569</t>
+          <t>https://m.place.naver.com/place/532361433</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1872,25 +1880,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>짐프라이빗 PT</t>
+          <t>마블피트니스 헬스&amp;PT 부산대장전점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sungeun1213@naver.com</t>
+          <t>lsh20220@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1416-9683</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부산대학로64번길 128 2층 짐프라이빗</t>
+          <t>부산광역시 금정구 중앙대로1719번길 47 2층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gymprivate_420</t>
+          <t>https://blog.naver.com/lsh20220</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1905,7 +1917,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1916,7 +1928,7 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1925,13 +1937,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>115</v>
+        <v>213</v>
       </c>
       <c r="Q16" t="n">
-        <v>23</v>
+        <v>151</v>
       </c>
       <c r="R16" t="n">
-        <v>138</v>
+        <v>364</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1940,51 +1952,51 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1928034806</t>
+          <t>2024917216</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1928034806</t>
+          <t>https://m.place.naver.com/place/2024917216</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>우성레포츠</t>
+          <t>메디앤컬필라테스 온천장점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>jgkim216@naver.com</t>
+          <t>medincurl_official@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>051-514-7755</t>
+          <t>0507-1440-3498</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로555번길 25 우성레포츠</t>
+          <t>부산광역시 금정구 온천장로 136-1 5층 메디앤컬필라테스 온천장점</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.medincurl.com/</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1994,7 +2006,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2015,17 +2027,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2</v>
+        <v>476</v>
       </c>
       <c r="Q17" t="n">
-        <v>9</v>
+        <v>395</v>
       </c>
       <c r="R17" t="n">
-        <v>11</v>
+        <v>871</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2034,51 +2046,51 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>13401019</t>
+          <t>1353161831</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13401019</t>
+          <t>https://m.place.naver.com/place/1353161831</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>수리,AS</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>헬스머신닥터</t>
+          <t>플러스짐 / 플러스휘트니스 헬스&amp;PT 서동점</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>mazzinggaj@naver.com</t>
+          <t>wntjdgh07@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1338-1262</t>
+          <t>051-711-1234</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로578번길 32 1층</t>
+          <t>부산광역시 금정구 서동로175번길 30 재원빌딩 2층,3층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mazzinggaj</t>
+          <t>https://blog.naver.com/wntjdgh07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2109,17 +2121,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>192</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2128,17 +2140,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1267557564</t>
+          <t>1903154613</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1267557564</t>
+          <t>https://m.place.naver.com/place/1903154613</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2150,29 +2162,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>씨투짐</t>
+          <t>DY휘트니스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cp8067@naver.com</t>
+          <t>04180801@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0507-1472-4133</t>
+          <t>0507-1444-3060</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로 1617-12 상가동 지하1층 102호</t>
+          <t>부산광역시 금정구 부곡온천천로 126 5층 DY휘트니스</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/cp8067</t>
+          <t>http://blog.naver.com/04180801</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2207,13 +2219,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="R19" t="n">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2222,51 +2234,51 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2015886126</t>
+          <t>16637799</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015886126</t>
+          <t>https://m.place.naver.com/place/16637799</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>유도장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>부산대 김사부 유도관</t>
+          <t>람보휘트니스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>lilianecosta@naver.com</t>
+          <t>gonasky@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>051-582-6565</t>
+          <t>051-529-0472</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금정로 72</t>
+          <t>부산광역시 금정구 금사로 88 3층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/ksb_judo/?hl=ko</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2276,7 +2288,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2297,18 +2309,18 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
         <v>15</v>
       </c>
-      <c r="Q20" t="n">
-        <v>14</v>
-      </c>
-      <c r="R20" t="n">
-        <v>29</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>X</t>
@@ -2316,51 +2328,51 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1824414972</t>
+          <t>1071809078</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1824414972</t>
+          <t>https://m.place.naver.com/place/1071809078</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SNPE 부산대점</t>
+          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>tasin@naver.com</t>
+          <t>healthstargym01@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1321-9238</t>
+          <t>0507-1395-8189</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부산대학로 29 2층 SNPE 부산대점</t>
+          <t>부산광역시 금정구 구서로 12 2층 헬스스타짐 구서점</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tasin</t>
+          <t>https://blog.naver.com/healthstargym01</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2391,17 +2403,17 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>384</v>
+        <v>80</v>
       </c>
       <c r="Q21" t="n">
-        <v>367</v>
+        <v>149</v>
       </c>
       <c r="R21" t="n">
-        <v>751</v>
+        <v>229</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2410,51 +2422,51 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1547731644</t>
+          <t>2086997985</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1547731644</t>
+          <t>https://m.place.naver.com/place/2086997985</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>퓨어핏</t>
+          <t>위드피트니스 &amp; PT 부산대점</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>purefit89@naver.com</t>
+          <t>withfitness@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0507-1402-6402</t>
+          <t>0507-1397-4887</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 수림로20번길 36 5,6층(부곡동)</t>
+          <t>부산광역시 금정구 부산대학로 10 대우아파트 상가 위드피트니스 헬스장</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/purefit89</t>
+          <t>https://blog.naver.com/withfitness</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2485,17 +2497,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>1166</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>1700</v>
       </c>
       <c r="R22" t="n">
-        <v>25</v>
+        <v>2866</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
@@ -2504,51 +2516,51 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1362785918</t>
+          <t>13415160</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1362785918</t>
+          <t>https://m.place.naver.com/place/13415160</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>런던짐 프리미엄 헬스/PT</t>
+          <t>FR필라테스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>london_gym@naver.com</t>
+          <t>manhattan80@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1319-7187</t>
+          <t>0507-1336-9911</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 231 Z존빌딩 4층 런던짐</t>
+          <t>부산광역시 금정구 중앙대로1841번길 23 현대타운 8층 FR 필라테스</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/london_gym</t>
+          <t>https://blog.naver.com/manhattan80</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2579,17 +2591,17 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="Q23" t="n">
-        <v>136</v>
+        <v>35</v>
       </c>
       <c r="R23" t="n">
-        <v>264</v>
+        <v>111</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2598,51 +2610,51 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>2087177068</t>
+          <t>1828160442</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2087177068</t>
+          <t>https://m.place.naver.com/place/1828160442</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BT비티아시바피티아시바파이프가설자재판매임대설치</t>
+          <t>피트니스인앤스타 헬스&amp;PT&amp;스피닝</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>inanstarbusandae@naver.com</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>070-4594-0172</t>
+          <t>0507-1366-0046</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 노포동</t>
+          <t>부산광역시 금정구 중앙대로1685번길 7 피트니스인앤스타 2층</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/belief_s_im</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2652,7 +2664,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2673,17 +2685,17 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>801</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1318</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2119</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -2692,17 +2704,17 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>1751975582</t>
+          <t>1044450403</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1751975582</t>
+          <t>https://m.place.naver.com/place/1044450403</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2714,25 +2726,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>구서동큐브짐 헬스&amp;PT</t>
+          <t>워너짐 부산대</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cubegym_@naver.com</t>
+          <t>wannagym87@naver.com</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0507-1313-1519</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 구서중앙로15번길 20 승산스포렉스 건물 4층 헬스장</t>
+          <t>부산광역시 금정구 금강로 252-1 지하1층</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cubegym.guseo?igsh=dWx2NGJ6bDFqM3Zx&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/wannagym9_busanuni</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2767,13 +2783,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>47</v>
+        <v>592</v>
       </c>
       <c r="Q25" t="n">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="R25" t="n">
-        <v>176</v>
+        <v>625</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -2782,17 +2798,17 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1706540567</t>
+          <t>1046756058</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1706540567</t>
+          <t>https://m.place.naver.com/place/1046756058</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -2804,29 +2820,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>스카이짐 24H &amp; 기구필라테스</t>
+          <t>우성레포츠</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>skygym99@naver.com</t>
+          <t>yena0512@naver.com</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0507-1484-5661</t>
+          <t>051-514-7755</t>
         </is>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 441 7층 8층 9층</t>
+          <t>부산광역시 금정구 금강로555번길 25 우성레포츠</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>http://www.skygym.co.kr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2836,7 +2852,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2861,13 +2877,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2704</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="R26" t="n">
-        <v>2819</v>
+        <v>11</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -2876,51 +2892,51 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1730198934</t>
+          <t>13401019</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730198934</t>
+          <t>https://m.place.naver.com/place/13401019</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>다이어트,비만</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>웰니스점핑</t>
+          <t>근의공식GYM</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>adam2400@naver.com</t>
+          <t>muscleformula@naver.com</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>051-513-1588</t>
+          <t>0507-1455-7379</t>
         </is>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 494 구서골드 3상가 5층</t>
+          <t>부산광역시 금정구 금강로 389 4층</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/adam2400</t>
+          <t>https://blog.naver.com/muscleformula</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2955,13 +2971,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2970,47 +2986,51 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1219277187</t>
+          <t>2077635933</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1219277187</t>
+          <t>https://m.place.naver.com/place/2077635933</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>유도장</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>부산레포츠</t>
+          <t>부산대 김사부 유도관</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>songyum84@naver.com</t>
+          <t>sangwoo4386hr@naver.com</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>051-582-6565</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로335번길 43</t>
+          <t>부산광역시 금정구 금정로 72</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>http://051-582-8787.okqr.co.kr</t>
+          <t>https://www.instagram.com/ksb_judo/?hl=ko</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3041,17 +3061,17 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="Q28" t="n">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="R28" t="n">
-        <v>234</v>
+        <v>29</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -3060,47 +3080,51 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>11781881</t>
+          <t>1824414972</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11781881</t>
+          <t>https://m.place.naver.com/place/1824414972</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>스마트짐 구서점</t>
+          <t>핏머슬짐 남산동pt 남산동재활운동</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>syjkmk0504@naver.com</t>
+          <t>fit_muscle__gym@naver.com</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1347-4634</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1841번길 91 3층</t>
+          <t>부산광역시 금정구 청룡로 43 도순빌딩 2층</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://linktr.ee/smartgymguseo1</t>
+          <t>https://www.instagram.com/_fit_muscle__gym</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3131,17 +3155,17 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="Q29" t="n">
-        <v>232</v>
+        <v>15</v>
       </c>
       <c r="R29" t="n">
-        <v>297</v>
+        <v>33</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
@@ -3150,51 +3174,47 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1923851509</t>
+          <t>1073265057</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1923851509</t>
+          <t>https://m.place.naver.com/place/1073265057</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>유도장</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>윤피티앤짐</t>
+          <t>부곡 김사부 유도관</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>yunpt-gym@naver.com</t>
+          <t>dusilyura@naver.com</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0507-1391-9943</t>
-        </is>
-      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부산대학로49번길 33-3 1층 좌측</t>
+          <t>부산광역시 금정구 부곡로 169</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yunpt-gym</t>
+          <t>https://www.instagram.com/ksb_judo/</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3209,7 +3229,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3225,17 +3245,17 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>93</v>
+        <v>10</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -3244,17 +3264,17 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>1010289296</t>
+          <t>1783241619</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1010289296</t>
+          <t>https://m.place.naver.com/place/1783241619</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3266,29 +3286,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>헬스스타짐 헬스&amp;PT&amp;스피닝 구서점</t>
+          <t>윤피티앤짐</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>healthstargym01@naver.com</t>
+          <t>yunpt-gym@naver.com</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0507-1395-8189</t>
+          <t>0507-1391-9943</t>
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 구서로 12 2층 헬스스타짐 구서점</t>
+          <t>부산광역시 금정구 부산대학로49번길 33-3 1층 좌측</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthstargym01</t>
+          <t>https://blog.naver.com/yunpt-gym</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3323,13 +3343,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="Q31" t="n">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="R31" t="n">
-        <v>215</v>
+        <v>93</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
@@ -3338,17 +3358,17 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>2086997985</t>
+          <t>1010289296</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2086997985</t>
+          <t>https://m.place.naver.com/place/1010289296</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3360,29 +3380,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>리즈핏PT 장전점</t>
+          <t>제이디피트니스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>lizpit@naver.com</t>
+          <t>dkdltm895@naver.com</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0507-1346-4236</t>
+          <t>0507-1377-3447</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 수림로 17 찬지빌 5층</t>
+          <t>부산광역시 금정구 금강로565번길 26 지하1층</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/liz_fit_captain/</t>
+          <t>https://www.instagram.com/jd_.fit</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3417,13 +3437,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="Q32" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="R32" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3432,17 +3452,17 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1454971861</t>
+          <t>1164508746</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1454971861</t>
+          <t>https://m.place.naver.com/place/1164508746</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -3454,29 +3474,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>비너스짐</t>
+          <t>스마트짐 구서점</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>iamjollykim@naver.com</t>
+          <t>syjkmk0504@naver.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0507-1464-6250</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부산대학로 31 3,4층</t>
+          <t>부산광역시 금정구 중앙대로1841번길 91 3층</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/venusgym.busan</t>
+          <t>https://linktr.ee/smartgymguseo1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3507,17 +3523,17 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>199</v>
+        <v>65</v>
       </c>
       <c r="Q33" t="n">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="R33" t="n">
-        <v>404</v>
+        <v>298</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
@@ -3526,56 +3542,56 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1858723770</t>
+          <t>1923851509</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1858723770</t>
+          <t>https://m.place.naver.com/place/1923851509</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>위너피티</t>
+          <t>오성피트니스 헬스,PT&amp;필라테스 구서점</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>winner9295@naver.com</t>
+          <t>hakunashop@naver.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0507-1305-9297</t>
+          <t>0507-1458-5563</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1841번길 35 4층 위너피티</t>
+          <t>부산광역시 금정구 금강로 528 7층, 8층 오성피트니스 구서점</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_GwBZxj/chat</t>
+          <t>http://www.instagram.com/osungfitness_guseo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3596,7 +3612,7 @@
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3605,13 +3621,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>123</v>
+        <v>895</v>
       </c>
       <c r="Q34" t="n">
-        <v>127</v>
+        <v>342</v>
       </c>
       <c r="R34" t="n">
-        <v>250</v>
+        <v>1237</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -3620,51 +3636,51 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1882901584</t>
+          <t>1131532901</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1882901584</t>
+          <t>https://m.place.naver.com/place/1131532901</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>오성피트니스 헬스,PT&amp;필라테스 구서점</t>
+          <t>아이라이크핏</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hakunashop@naver.com</t>
+          <t>hc0music@naver.com</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0507-1458-5563</t>
+          <t>0507-1349-7781</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 528 7층, 8층 오성피트니스 구서점</t>
+          <t>부산광역시 금정구 금정로 185 2층</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/osungfitness_guseo</t>
+          <t>https://blog.naver.com/hc0music</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -3679,7 +3695,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3690,7 +3706,7 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3699,13 +3715,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>890</v>
+        <v>46</v>
       </c>
       <c r="Q35" t="n">
-        <v>342</v>
+        <v>21</v>
       </c>
       <c r="R35" t="n">
-        <v>1232</v>
+        <v>67</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3714,47 +3730,51 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1131532901</t>
+          <t>1053373474</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1131532901</t>
+          <t>https://m.place.naver.com/place/1053373474</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>체육관</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>위 트레이닝 PT스튜디오 부산대점</t>
+          <t>바벨하우스 남산</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>wetrainingstudio@naver.com</t>
+          <t>kl95y@naver.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0507-1312-7354</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 장전온천천로 51 테라스파크 4층 408호</t>
+          <t>부산광역시 금정구 중앙대로 2027 새생명빌딩 지하1층</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wetrainingstudio</t>
+          <t>https://blog.naver.com/kl95y</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3789,13 +3809,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>509</v>
+        <v>22</v>
       </c>
       <c r="Q36" t="n">
-        <v>219</v>
+        <v>12</v>
       </c>
       <c r="R36" t="n">
-        <v>728</v>
+        <v>34</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -3804,61 +3824,61 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1393812362</t>
+          <t>1153442485</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1393812362</t>
+          <t>https://m.place.naver.com/place/1153442485</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>다이어트,샐러드</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>짐핏부산2</t>
+          <t>열정샐러드</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>koolerk@naver.com</t>
+          <t>lovejh5987@naver.com</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0507-1489-3395</t>
+          <t>0507-1380-5130</t>
         </is>
       </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 271-5 2층</t>
+          <t>부산광역시 금정구 중앙대로1841번길 65 B1 열정샐러드</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/WSW6UZO</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -3868,14 +3888,10 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsw6uzo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>X</t>
@@ -3887,13 +3903,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
@@ -3902,51 +3918,47 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>2004016709</t>
+          <t>1563038425</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2004016709</t>
+          <t>https://m.place.naver.com/place/1563038425</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>블랙바디짐</t>
+          <t>하이킥스 그룹PT 부산대 장전점</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>july7609@naver.com</t>
+          <t>hykickspnu@naver.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0507-1387-4009</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금정로149번길 8 2층</t>
+          <t>부산광역시 금정구 부곡온천천로 126 4층</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/july7609</t>
+          <t>https://www.instagram.com/hykicks_pnu/</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3961,7 +3973,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3981,13 +3993,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="Q38" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="R38" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -3996,51 +4008,51 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>38595474</t>
+          <t>2029378419</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38595474</t>
+          <t>https://m.place.naver.com/place/2029378419</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>근의공식GYM</t>
+          <t>멋짐 헬스&amp;PT 구서점</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>muscleformula@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0507-1455-7379</t>
+          <t>0507-1483-8689</t>
         </is>
       </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 389 4층</t>
+          <t>부산광역시 금정구 두실로 5 2층</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/muscleformula</t>
+          <t>https://blog.naver.com/mutgym_</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4071,17 +4083,17 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>5</v>
+        <v>806</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>438</v>
       </c>
       <c r="R39" t="n">
-        <v>7</v>
+        <v>1244</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -4090,65 +4102,61 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>2077635933</t>
+          <t>1982277371</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2077635933</t>
+          <t>https://m.place.naver.com/place/1982277371</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>스포츠센터</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>어댑핏스튜디오 부산점</t>
+          <t>모션업PT 온천장점</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>adapfit_busan@naver.com</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>lab@adapfit.kr</t>
-        </is>
-      </c>
+          <t>rehab_coach@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>051-746-1152</t>
+          <t>0507-1488-3306</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금샘로 361 3층~4층</t>
+          <t>부산광역시 금정구 온천장로 136-1 6층 모션업PT</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://youtube.com/@adapfit?si=LZjvbctvSj0vLRzM</t>
+          <t>https://booking.naver.com/booking/6/bizes/765659</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -4173,13 +4181,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="Q40" t="n">
-        <v>534</v>
+        <v>476</v>
       </c>
       <c r="R40" t="n">
-        <v>566</v>
+        <v>639</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
@@ -4188,51 +4196,47 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>1861035294</t>
+          <t>1670613112</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1861035294</t>
+          <t>https://m.place.naver.com/place/1670613112</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>허그짐 구서점 헬스&amp;PT</t>
+          <t>리온피티</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>huggym_guseo@naver.com</t>
+          <t>cestvalerie@naver.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0507-1316-7789</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 503 롯데캐슬상가 4층</t>
+          <t>부산광역시 금정구 금정로 80-1 지하1층</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/huggym_guseo</t>
+          <t>https://www.instagram.com/reon__pt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4247,7 +4251,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4267,13 +4271,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="Q41" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="R41" t="n">
-        <v>210</v>
+        <v>86</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -4282,51 +4286,51 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2015222427</t>
+          <t>1151366943</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2015222427</t>
+          <t>https://m.place.naver.com/place/1151366943</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>수리,AS</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>멋짐 헬스&amp;PT 구서점</t>
+          <t>헬스머신닥터</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>mazzinggaj@naver.com</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0507-1483-8689</t>
+          <t>0507-1338-1262</t>
         </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 두실로 5 2층</t>
+          <t>부산광역시 금정구 금강로578번길 32 1층</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym_</t>
+          <t>https://blog.naver.com/mazzinggaj</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4357,17 +4361,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>782</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>435</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>1217</v>
+        <v>1</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -4376,51 +4380,51 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1982277371</t>
+          <t>1267557564</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1982277371</t>
+          <t>https://m.place.naver.com/place/1267557564</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>포레스트짐</t>
+          <t>일레븐핏 부산대점</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>kja00710@naver.com</t>
+          <t>elevenfit@naver.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>051-583-7674</t>
+          <t>0507-1495-7982</t>
         </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 장전로12번길 45</t>
+          <t>부산광역시 금정구 금강로 209 한신시티빌 B1F</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forestgym__pt/</t>
+          <t>https://blog.naver.com/elevenfit</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4435,7 +4439,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4455,13 +4459,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>750</v>
       </c>
       <c r="R43" t="n">
-        <v>12</v>
+        <v>884</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -4470,51 +4474,51 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>1637213319</t>
+          <t>1356064248</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1637213319</t>
+          <t>https://m.place.naver.com/place/1356064248</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>기업</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>피티인사이트</t>
+          <t>SNPE 부산대점</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>pt-insight@naver.com</t>
+          <t>tasin@naver.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>070-4814-1947</t>
+          <t>0507-1321-9238</t>
         </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1959번길 8</t>
+          <t>부산광역시 금정구 부산대학로 29 2층 SNPE 부산대점</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/tasin</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4524,12 +4528,12 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4545,17 +4549,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>371</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>755</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -4564,51 +4568,51 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>78348638</t>
+          <t>1547731644</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/78348638</t>
+          <t>https://m.place.naver.com/place/1547731644</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>플러스짐 / 플러스휘트니스 헬스&amp;PT 서동점</t>
+          <t>퍼스트핏</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>wntjdgh07@naver.com</t>
+          <t>ysl8900@naver.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>051-711-1234</t>
+          <t>051-949-8979</t>
         </is>
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 서동로175번길 30 재원빌딩 2층,3층</t>
+          <t>부산광역시 금정구 장전로 8 1층</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wntjdgh07</t>
+          <t>https://www.instagram.com/first_fit__</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4623,7 +4627,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4643,13 +4647,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>134</v>
+        <v>11</v>
       </c>
       <c r="Q45" t="n">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="R45" t="n">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
@@ -4658,51 +4662,51 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>1903154613</t>
+          <t>1507156227</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1903154613</t>
+          <t>https://m.place.naver.com/place/1507156227</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에스짐 부곡점</t>
+          <t>BT비티아시바피티아시바파이프가설자재판매임대설치</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>s_gym_3@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0507-1340-2227</t>
+          <t>070-4594-0172</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 오시게로12번길 23 3층</t>
+          <t>부산광역시 금정구 노포동</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/s_gym_3</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4712,12 +4716,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4733,17 +4737,17 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -4752,17 +4756,17 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>1224508416</t>
+          <t>1751975582</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1224508416</t>
+          <t>https://m.place.naver.com/place/1751975582</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4774,29 +4778,29 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>람보휘트니스</t>
+          <t>씨투짐</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>gonasky@naver.com</t>
+          <t>cp8067@naver.com</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>051-529-0472</t>
+          <t>0507-1472-4133</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금사로 88 3층</t>
+          <t>부산광역시 금정구 중앙대로 1617-12 상가동 지하1층 102호</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/cp8067</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4806,12 +4810,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4827,17 +4831,17 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P47" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q47" t="n">
         <v>10</v>
       </c>
-      <c r="Q47" t="n">
-        <v>5</v>
-      </c>
       <c r="R47" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -4846,51 +4850,51 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>1071809078</t>
+          <t>2015886126</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1071809078</t>
+          <t>https://m.place.naver.com/place/2015886126</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>체육관</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>바벨하우스 남산</t>
+          <t>닥터핏24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>kl95y@naver.com</t>
+          <t>drf24@naver.com</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0507-1312-7354</t>
+          <t>051-710-8006</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로 2027 새생명빌딩 지하1층</t>
+          <t>부산광역시 금정구 중앙대로 1829 12층 닥터핏24, 13층 닥터골프</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kl95y</t>
+          <t>https://drfit24-golf.com/</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4905,7 +4909,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4925,13 +4929,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="Q48" t="n">
-        <v>12</v>
+        <v>351</v>
       </c>
       <c r="R48" t="n">
-        <v>34</v>
+        <v>364</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -4940,17 +4944,17 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>1153442485</t>
+          <t>1696181456</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1153442485</t>
+          <t>https://m.place.naver.com/place/1696181456</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -4962,29 +4966,29 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>어썸바디PT</t>
+          <t>라이트짐 헬스&amp;PT 장전점</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>awesomebody_pt@naver.com</t>
+          <t>weejae0420@naver.com</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0507-1389-5382</t>
+          <t>0507-1361-2316</t>
         </is>
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금정로 62 청암타워 5층 어썸바디PT</t>
+          <t>부산광역시 금정구 중앙대로1719번길 23 우남빌딩 6층 601호 라이트짐</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>http://instagram.com/awesomebody_pt_studio</t>
+          <t>https://www.instagram.com/rightgym_pnu</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5019,13 +5023,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>25</v>
+        <v>737</v>
       </c>
       <c r="Q49" t="n">
-        <v>74</v>
+        <v>283</v>
       </c>
       <c r="R49" t="n">
-        <v>99</v>
+        <v>1020</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -5034,51 +5038,51 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1730533003</t>
+          <t>1184810796</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1730533003</t>
+          <t>https://m.place.naver.com/place/1184810796</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>반반피트니스 헬스&amp;PT</t>
+          <t>리즈핏PT 장전점</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>b_b__fitness@naver.com</t>
+          <t>lizpit@naver.com</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>051-532-9682</t>
+          <t>0507-1346-4236</t>
         </is>
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 서동중심로 62 3층</t>
+          <t>부산광역시 금정구 수림로 17 찬지빌 5층</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/liz_fit_captain/</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5088,7 +5092,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5109,17 +5113,17 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1110</v>
+        <v>48</v>
       </c>
       <c r="Q50" t="n">
-        <v>215</v>
+        <v>45</v>
       </c>
       <c r="R50" t="n">
-        <v>1325</v>
+        <v>93</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -5128,47 +5132,51 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1825995735</t>
+          <t>1454971861</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1825995735</t>
+          <t>https://m.place.naver.com/place/1454971861</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>현대휘트니스PT</t>
+          <t>스마트핏 구서점</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>judosabumnim@naver.com</t>
+          <t>yujin2416@naver.com</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>051-949-0110</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부곡로 79 탑마트2층(헬스)최고주차시설</t>
+          <t>부산광역시 금정구 중앙대로1841번길 91 마루빌딩 2층</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/judosabumnim</t>
+          <t>https://linktr.ee/smartfit_guseo</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5203,13 +5211,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>862</v>
       </c>
       <c r="R51" t="n">
-        <v>2</v>
+        <v>907</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -5218,17 +5226,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>1139656325</t>
+          <t>36271098</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1139656325</t>
+          <t>https://m.place.naver.com/place/36271098</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5240,29 +5248,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>피트니스인앤스타 헬스&amp;PT&amp;스피닝</t>
+          <t>짐프라이빗 PT</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>inanstarbusandae@naver.com</t>
+          <t>sungeun1213@naver.com</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0507-1366-0046</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1685번길 7 피트니스인앤스타 2층</t>
+          <t>부산광역시 금정구 부산대학로64번길 128 2층 짐프라이빗</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/belief_s_im</t>
+          <t>https://www.instagram.com/gymprivate_420</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5288,7 +5292,7 @@
       <c r="M52" t="inlineStr"/>
       <c r="N52" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5297,13 +5301,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>787</v>
+        <v>115</v>
       </c>
       <c r="Q52" t="n">
-        <v>1307</v>
+        <v>23</v>
       </c>
       <c r="R52" t="n">
-        <v>2094</v>
+        <v>138</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -5312,51 +5316,51 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>1044450403</t>
+          <t>1928034806</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1044450403</t>
+          <t>https://m.place.naver.com/place/1928034806</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>핏핏바디트레이닝 PT센터 부산대점</t>
+          <t>무지개휘트니스 남산점PT&amp;필라테스&amp;요가&amp;줌바</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>fitfitness@naver.com</t>
+          <t>rainbow4441@naver.com</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0507-1404-5838</t>
+          <t>0507-1442-4445</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 209-1 3층 301호</t>
+          <t>부산광역시 금정구 금강로 700 남산빌딩 4층 무지개휘트니스</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitfitness</t>
+          <t>https://blog.naver.com/rainbow4441</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5391,13 +5395,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>148</v>
+        <v>887</v>
       </c>
       <c r="Q53" t="n">
-        <v>201</v>
+        <v>876</v>
       </c>
       <c r="R53" t="n">
-        <v>349</v>
+        <v>1763</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -5406,17 +5410,17 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>736873028</t>
+          <t>381975477</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/736873028</t>
+          <t>https://m.place.naver.com/place/381975477</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5428,34 +5432,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>모션업PT 구서 4호점</t>
+          <t>짐핏부산2</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>motionuppt2879@naver.com</t>
+          <t>lgv3v4v5@naver.com</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0507-1306-1256</t>
+          <t>0507-1489-3395</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 구서로 3 3층 모션업PT</t>
+          <t>부산광역시 금정구 금강로 271-5 2층</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/motionuppt2879</t>
+          <t>https://talk.naver.com/WSW6UZO</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -5465,15 +5469,19 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsw6uzo</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr">
         <is>
           <t>X</t>
@@ -5481,17 +5489,17 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="Q54" t="n">
-        <v>218</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>331</v>
+        <v>4</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -5500,17 +5508,17 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>1537157184</t>
+          <t>2004016709</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1537157184</t>
+          <t>https://m.place.naver.com/place/2004016709</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5522,29 +5530,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>워너짐 부산대</t>
+          <t>블랙바디짐</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>wannagym87@naver.com</t>
+          <t>july7609@naver.com</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0507-1313-1519</t>
+          <t>0507-1387-4009</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 252-1 지하1층</t>
+          <t>부산광역시 금정구 금정로149번길 8 2층</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/wannagym9_busanuni</t>
+          <t>https://blog.naver.com/july7609</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5559,7 +5567,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5579,13 +5587,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>586</v>
+        <v>49</v>
       </c>
       <c r="Q55" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R55" t="n">
-        <v>619</v>
+        <v>81</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -5594,51 +5602,51 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>1046756058</t>
+          <t>38595474</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1046756058</t>
+          <t>https://m.place.naver.com/place/38595474</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>칼리스핏 PT 부산대점</t>
+          <t>런던짐 프리미엄 헬스/PT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>calicefit@naver.com</t>
+          <t>london_gym@naver.com</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0507-1477-1315</t>
+          <t>0507-1319-7187</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 247-5 4층 칼리스핏 PT</t>
+          <t>부산광역시 금정구 금강로 231 Z존빌딩 4층 런던짐</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sx3H6arh</t>
+          <t>https://blog.naver.com/london_gym</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5653,7 +5661,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5664,7 +5672,7 @@
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5673,13 +5681,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>41</v>
+        <v>129</v>
       </c>
       <c r="Q56" t="n">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="R56" t="n">
-        <v>187</v>
+        <v>265</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5688,51 +5696,51 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1891006830</t>
+          <t>2087177068</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1891006830</t>
+          <t>https://m.place.naver.com/place/2087177068</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>바디퀄리티</t>
+          <t>스카이짐 24H &amp; 기구필라테스</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>zoosoo4@naver.com</t>
+          <t>skygym99@naver.com</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0507-1375-2643</t>
+          <t>0507-1484-5661</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로 1632 . 3층</t>
+          <t>부산광역시 금정구 금강로 441 7층 8층 9층</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_lxnxhaxj</t>
+          <t>http://www.skygym.co.kr</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5747,7 +5755,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5758,22 +5766,22 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>204</v>
+        <v>2707</v>
       </c>
       <c r="Q57" t="n">
-        <v>65</v>
+        <v>118</v>
       </c>
       <c r="R57" t="n">
-        <v>269</v>
+        <v>2825</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -5782,17 +5790,17 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>1346534434</t>
+          <t>1730198934</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346534434</t>
+          <t>https://m.place.naver.com/place/1730198934</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -5804,34 +5812,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>라이트짐 장전역점</t>
+          <t>위너피티</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bderpccis@naver.com</t>
+          <t>winner9295@naver.com</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0507-1361-2316</t>
+          <t>0507-1305-9297</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1719번길 23 우남빌딩 6층 601호 라이트짐</t>
+          <t>부산광역시 금정구 중앙대로1841번길 35 4층 위너피티</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/rightgym_pnu</t>
+          <t>http://pf.kakao.com/_GwBZxj/chat</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5852,7 +5860,7 @@
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5861,13 +5869,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>725</v>
+        <v>123</v>
       </c>
       <c r="Q58" t="n">
-        <v>276</v>
+        <v>127</v>
       </c>
       <c r="R58" t="n">
-        <v>1001</v>
+        <v>250</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -5876,51 +5884,51 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>1184810796</t>
+          <t>1882901584</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1184810796</t>
+          <t>https://m.place.naver.com/place/1882901584</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>시각디자인</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>위너스피티</t>
+          <t>하와이피티</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>winnerspt@naver.com</t>
+          <t>whwlgns83@naver.com</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>051-904-7315</t>
+          <t>0507-1301-0781</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1959번길 8 3층</t>
+          <t>부산광역시 금정구 중앙대로1719번길 56 b1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/winnerspt</t>
+          <t>https://blog.naver.com/whwlgns83</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5951,17 +5959,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -5970,61 +5978,61 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>13466460</t>
+          <t>1475186578</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13466460</t>
+          <t>https://m.place.naver.com/place/1475186578</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>장례</t>
+          <t>기업</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>피티상조</t>
+          <t>피티인사이트</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>spesgym@naver.com</t>
+          <t>pt-insight@naver.com</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1800-0124</t>
+          <t>070-4814-1947</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 구서중앙로40번길 51 1층</t>
+          <t>부산광역시 금정구 중앙대로1959번길 8</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.pt-life.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -6064,51 +6072,51 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>36886387</t>
+          <t>78348638</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36886387</t>
+          <t>https://m.place.naver.com/place/78348638</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>퍼스트핏</t>
+          <t>천지연피트니스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ysl8900@naver.com</t>
+          <t>cjy98501@naver.com</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>051-949-8979</t>
+          <t>0507-1363-9851</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 장전로 8 1층</t>
+          <t>부산광역시 금정구 부곡온천천로 126 삼승렉스풀 상가2층</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/first_fit__</t>
+          <t>https://blog.naver.com/cjy98501</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -6123,7 +6131,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6143,13 +6151,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="Q61" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="R61" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -6158,17 +6166,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>1507156227</t>
+          <t>1458862347</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1507156227</t>
+          <t>https://m.place.naver.com/place/1458862347</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6180,29 +6188,29 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>더매력짐&amp;기구필라테스</t>
+          <t>짐핏 부산</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>tmrgym1716@naver.com</t>
+          <t>lgv3v4v5@naver.com</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0507-1419-6678</t>
+          <t>0507-1333-0826</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부곡로 50</t>
+          <t>부산광역시 금정구 수림로85번길 53 2층, 3층</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/tmrgym1716</t>
+          <t>https://www.instagram.com/gymfit.yh</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -6217,7 +6225,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -6237,13 +6245,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>189</v>
+        <v>4</v>
       </c>
       <c r="Q62" t="n">
-        <v>551</v>
+        <v>11</v>
       </c>
       <c r="R62" t="n">
-        <v>740</v>
+        <v>15</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -6252,17 +6260,17 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>1639193921</t>
+          <t>1005096569</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1639193921</t>
+          <t>https://m.place.naver.com/place/1005096569</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6274,29 +6282,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>알투피 운동과학</t>
+          <t>칼리스핏 PT 부산대점</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>dream_dept@naver.com</t>
+          <t>calicefit@naver.com</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0507-1472-6302</t>
+          <t>0507-1477-1315</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금샘로485번길 65 B동 223호</t>
+          <t>부산광역시 금정구 금강로 247-5 4층 칼리스핏 PT</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://open.kakao.com/o/sx3H6arh</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6306,7 +6314,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6322,22 +6330,22 @@
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>147</v>
       </c>
       <c r="R63" t="n">
-        <v>3</v>
+        <v>189</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
@@ -6346,17 +6354,17 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>1993180780</t>
+          <t>1891006830</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1993180780</t>
+          <t>https://m.place.naver.com/place/1891006830</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6368,25 +6376,29 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>옐로우피티</t>
+          <t>어썸바디PT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ysm0492@naver.com</t>
+          <t>awesomebody_pt@naver.com</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0507-1389-5382</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 246 1층 옐로우피티</t>
+          <t>부산광역시 금정구 금정로 62 청암타워 5층 어썸바디PT</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ysm0492</t>
+          <t>http://instagram.com/awesomebody_pt_studio</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6401,7 +6413,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -6421,13 +6433,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="Q64" t="n">
-        <v>184</v>
+        <v>70</v>
       </c>
       <c r="R64" t="n">
-        <v>281</v>
+        <v>95</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
@@ -6436,17 +6448,17 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>1117462699</t>
+          <t>1730533003</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1117462699</t>
+          <t>https://m.place.naver.com/place/1730533003</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6458,29 +6470,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>일레븐핏 부산대점</t>
+          <t>구서동큐브짐 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>elevenfit@naver.com</t>
+          <t>cubegym_@naver.com</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>0507-1495-7982</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로 209 한신시티빌 B1F</t>
+          <t>부산광역시 금정구 구서중앙로15번길 20 승산스포렉스 건물 4층 헬스장</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/elevenfit</t>
+          <t>https://www.instagram.com/cubegym.guseo?igsh=dWx2NGJ6bDFqM3Zx&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -6495,7 +6503,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -6515,13 +6523,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>134</v>
+        <v>47</v>
       </c>
       <c r="Q65" t="n">
-        <v>749</v>
+        <v>129</v>
       </c>
       <c r="R65" t="n">
-        <v>883</v>
+        <v>176</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -6530,17 +6538,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>1356064248</t>
+          <t>1706540567</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1356064248</t>
+          <t>https://m.place.naver.com/place/1706540567</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6552,29 +6560,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>범어휘트니스</t>
+          <t>NSgym</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>jfitness-@naver.com</t>
+          <t>rocksr1945@naver.com</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0507-1406-1969</t>
+          <t>0507-1422-2918</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로 2096 1층 범어휘트니스 by j.f.c</t>
+          <t>부산광역시 금정구 중앙대로 2049 3, 4층</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jfitness-</t>
+          <t>https://www.instagram.com/nsgym7/</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6589,7 +6597,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -6609,13 +6617,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>384</v>
+        <v>96</v>
       </c>
       <c r="Q66" t="n">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="R66" t="n">
-        <v>491</v>
+        <v>178</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -6624,17 +6632,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>1512578499</t>
+          <t>1220858968</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1512578499</t>
+          <t>https://m.place.naver.com/place/1220858968</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6646,25 +6654,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>하이킥스 그룹PT 부산대 장전점</t>
+          <t>모션업PT 구서 4호점</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>hykickspnu@naver.com</t>
+          <t>motionuppt2879@naver.com</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>0507-1306-1256</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부곡온천천로 126 4층</t>
+          <t>부산광역시 금정구 구서로 3 3층 모션업PT</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/hykicks_pnu/</t>
+          <t>https://blog.naver.com/motionuppt2879</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6679,7 +6691,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -6699,13 +6711,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="Q67" t="n">
-        <v>17</v>
+        <v>215</v>
       </c>
       <c r="R67" t="n">
-        <v>47</v>
+        <v>328</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6714,65 +6726,61 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>2029378419</t>
+          <t>1537157184</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2029378419</t>
+          <t>https://m.place.naver.com/place/1537157184</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>메디앤컬필라테스 구서점</t>
+          <t>허그짐 구서점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>medincurl_official@naver.com</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>sample@sample.or.kr</t>
-        </is>
-      </c>
+          <t>huggym_guseo@naver.com</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0507-1469-3741</t>
+          <t>0507-1316-7789</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1841번길 35 7층 메디앤컬필라테스</t>
+          <t>부산광역시 금정구 금강로 503 롯데캐슬상가 4층</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>http://www.medincurl.com/</t>
+          <t>https://blog.naver.com/huggym_guseo</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -6788,7 +6796,7 @@
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6797,13 +6805,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>572</v>
+        <v>123</v>
       </c>
       <c r="Q68" t="n">
-        <v>257</v>
+        <v>93</v>
       </c>
       <c r="R68" t="n">
-        <v>829</v>
+        <v>216</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
@@ -6812,17 +6820,17 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>532361433</t>
+          <t>2015222427</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/532361433</t>
+          <t>https://m.place.naver.com/place/2015222427</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -6834,12 +6842,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>리온피티</t>
+          <t>옐로우피티</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>cestvalerie@naver.com</t>
+          <t>ysm0492@naver.com</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -6847,12 +6855,12 @@
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금정로 80-1 지하1층</t>
+          <t>부산광역시 금정구 금강로 246 1층 옐로우피티</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/reon__pt</t>
+          <t>https://blog.naver.com/ysm0492</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6867,7 +6875,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -6887,13 +6895,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>74</v>
+        <v>97</v>
       </c>
       <c r="Q69" t="n">
-        <v>10</v>
+        <v>184</v>
       </c>
       <c r="R69" t="n">
-        <v>84</v>
+        <v>281</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -6902,51 +6910,47 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>1151366943</t>
+          <t>1117462699</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1151366943</t>
+          <t>https://m.place.naver.com/place/1117462699</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>스마트핏 구서점</t>
+          <t>천보 퍼스널 스튜디오</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>syjkmk0504@naver.com</t>
+          <t>kwon7741@naver.com</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>051-949-0110</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1841번길 91 마루빌딩 2층</t>
+          <t>부산광역시 금정구 구서로 2</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://linktr.ee/smartfit_guseo</t>
+          <t>https://blog.naver.com/kwon7741</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6981,13 +6985,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="Q70" t="n">
-        <v>861</v>
+        <v>5</v>
       </c>
       <c r="R70" t="n">
-        <v>906</v>
+        <v>7</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -6996,17 +7000,17 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>36271098</t>
+          <t>37127323</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/36271098</t>
+          <t>https://m.place.naver.com/place/37127323</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7018,29 +7022,25 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>DY휘트니스</t>
+          <t>현대휘트니스PT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>04180801@naver.com</t>
+          <t>judosabumnim@naver.com</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>0507-1444-3060</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부곡온천천로 126 5층 DY휘트니스</t>
+          <t>부산광역시 금정구 부곡로 79 탑마트2층(헬스)최고주차시설</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>http://blog.naver.com/04180801</t>
+          <t>https://blog.naver.com/judosabumnim</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7071,17 +7071,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>105</v>
+        <v>2</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -7090,46 +7090,46 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>16637799</t>
+          <t>1139656325</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/16637799</t>
+          <t>https://m.place.naver.com/place/1139656325</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>다이어트,샐러드</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>열정샐러드</t>
+          <t>에이치코어운동센터</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>tirp2412@naver.com</t>
+          <t>thth806@naver.com</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0507-1380-5130</t>
+          <t>0507-1325-5168</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1841번길 65 B1 열정샐러드</t>
+          <t>부산광역시 금정구 금강로 514 3층</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7169,13 +7169,13 @@
         </is>
       </c>
       <c r="P72" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q72" t="n">
         <v>2</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -7184,51 +7184,51 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>1563038425</t>
+          <t>1437613013</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1563038425</t>
+          <t>https://m.place.naver.com/place/1437613013</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>메디앤컬필라테스 온천장점</t>
+          <t>현휘트니스</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>medincurl_official@naver.com</t>
+          <t>hyeonfitness@naver.com</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0507-1440-3498</t>
+          <t>0507-1333-1203</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 온천장로 136-1 5층 메디앤컬필라테스 온천장점</t>
+          <t>부산광역시 금정구 중앙대로 1617-12 2층</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.medincurl.com/</t>
+          <t>https://blog.naver.com/hyeonfitness</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7263,13 +7263,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>473</v>
+        <v>222</v>
       </c>
       <c r="Q73" t="n">
-        <v>394</v>
+        <v>204</v>
       </c>
       <c r="R73" t="n">
-        <v>867</v>
+        <v>426</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -7278,51 +7278,47 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>1353161831</t>
+          <t>1004485815</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1353161831</t>
+          <t>https://m.place.naver.com/place/1004485815</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FR필라테스</t>
+          <t>위 트레이닝 PT스튜디오 부산대점</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>manhattan80@naver.com</t>
+          <t>wetrainingstudio@naver.com</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>0507-1336-9911</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1841번길 23 현대타운 8층 FR 필라테스</t>
+          <t>부산광역시 금정구 장전온천천로 51 테라스파크 4층 408호</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/manhattan80</t>
+          <t>https://blog.naver.com/wetrainingstudio</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7353,17 +7349,17 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P74" t="n">
-        <v>76</v>
+        <v>511</v>
       </c>
       <c r="Q74" t="n">
-        <v>35</v>
+        <v>219</v>
       </c>
       <c r="R74" t="n">
-        <v>111</v>
+        <v>730</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -7372,51 +7368,47 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>1828160442</t>
+          <t>1393812362</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1828160442</t>
+          <t>https://m.place.naver.com/place/1393812362</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>핏핏바디트레이닝 PT센터 구서점</t>
+          <t>레고핏 피트니스 구서점</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>fitfitness@naver.com</t>
+          <t>luvrover99@naver.com</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>051-512-5818</t>
-        </is>
-      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1873번길 14 3층</t>
+          <t>부산광역시 금정구 중앙대로1929번길 11 유림빌딩 2층</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fitfitness</t>
+          <t>https://blog.naver.com/luvrover99</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -7451,13 +7443,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>212</v>
+        <v>299</v>
       </c>
       <c r="Q75" t="n">
-        <v>193</v>
+        <v>308</v>
       </c>
       <c r="R75" t="n">
-        <v>405</v>
+        <v>607</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
@@ -7466,17 +7458,17 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>38642628</t>
+          <t>1940991515</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/38642628</t>
+          <t>https://m.place.naver.com/place/1940991515</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7488,25 +7480,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>천보 퍼스널 스튜디오</t>
+          <t>J1휘트니스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>kwon7741@naver.com</t>
+          <t>knifesam1983@naver.com</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>051-518-6330</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 구서로 2</t>
+          <t>부산광역시 금정구 범어천로 4-1</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/kwon7741</t>
+          <t>https://blog.naver.com/knifesam1983</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -7541,10 +7537,10 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
         <v>7</v>
@@ -7556,17 +7552,17 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>37127323</t>
+          <t>35744238</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37127323</t>
+          <t>https://m.place.naver.com/place/35744238</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -7578,29 +7574,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>J1휘트니스</t>
+          <t>에스짐 부곡점</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>knifesam1983@naver.com</t>
+          <t>s_gym_3@naver.com</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>051-518-6330</t>
+          <t>0507-1340-2227</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 범어천로 4-1</t>
+          <t>부산광역시 금정구 오시게로12번길 23 3층</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/knifesam1983</t>
+          <t>https://blog.naver.com/s_gym_3</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -7631,17 +7627,17 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="Q77" t="n">
-        <v>4</v>
+        <v>244</v>
       </c>
       <c r="R77" t="n">
-        <v>7</v>
+        <v>354</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -7650,51 +7646,51 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>35744238</t>
+          <t>1224508416</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/35744238</t>
+          <t>https://m.place.naver.com/place/1224508416</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>맨하탄 필라테스&amp;헬스</t>
+          <t>퓨어핏</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>manhattan80@naver.com</t>
+          <t>purefit89@naver.com</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0507-1383-9711</t>
+          <t>0507-1402-6402</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1841번길 23 현대타운 8층</t>
+          <t>부산광역시 금정구 수림로20번길 36 5,6층(부곡동)</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/manhattan80</t>
+          <t>https://blog.naver.com/purefit89</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -7729,13 +7725,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>463</v>
+        <v>1</v>
       </c>
       <c r="Q78" t="n">
-        <v>199</v>
+        <v>24</v>
       </c>
       <c r="R78" t="n">
-        <v>662</v>
+        <v>25</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -7744,51 +7740,51 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>11663411</t>
+          <t>1362785918</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11663411</t>
+          <t>https://m.place.naver.com/place/1362785918</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>장례</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>대기구필라테스청담 서동점</t>
+          <t>피티상조</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>cjdeka0502@naver.com</t>
+          <t>spesgym@naver.com</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0507-1387-0018</t>
+          <t>1800-0124</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 서동로 168 9층</t>
+          <t>부산광역시 금정구 구서중앙로40번길 51 1층</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_txhfbG</t>
+          <t>https://www.pt-life.co.kr/</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -7814,22 +7810,22 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>484</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>422</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>906</v>
+        <v>0</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
@@ -7838,51 +7834,55 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>1651565560</t>
+          <t>36886387</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1651565560</t>
+          <t>https://m.place.naver.com/place/36886387</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠센터</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>이룸핏 헬스&amp;PT 온천장점</t>
+          <t>어댑핏스튜디오 부산점</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>erumfit0415@naver.com</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>adapfit_busan@naver.com</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>lab@adapfit.kr</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0507-1392-7832</t>
+          <t>051-746-1152</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 식물원로 25 3층 이룸핏 온천장점</t>
+          <t>부산광역시 금정구 금샘로 361 3층~4층</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/erumfit0415</t>
+          <t>https://youtube.com/@adapfit?si=LZjvbctvSj0vLRzM</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -7917,13 +7917,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>185</v>
+        <v>32</v>
       </c>
       <c r="Q80" t="n">
-        <v>519</v>
+        <v>536</v>
       </c>
       <c r="R80" t="n">
-        <v>704</v>
+        <v>568</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -7932,51 +7932,51 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>1124866804</t>
+          <t>1861035294</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1124866804</t>
+          <t>https://m.place.naver.com/place/1861035294</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>제이디피트니스</t>
+          <t>포레스트짐</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>dkdltm895@naver.com</t>
+          <t>kja00710@naver.com</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0507-1377-3447</t>
+          <t>051-583-7674</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금강로565번길 26 지하1층</t>
+          <t>부산광역시 금정구 장전로12번길 45</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/jd_.fit</t>
+          <t>https://www.instagram.com/forestgym__pt/</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="R81" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="S81" t="inlineStr">
         <is>
@@ -8026,51 +8026,51 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>1164508746</t>
+          <t>1637213319</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1164508746</t>
+          <t>https://m.place.naver.com/place/1637213319</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 부산대장전점</t>
+          <t>알투피 운동과학</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>lsh20220@naver.com</t>
+          <t>dream_dept@naver.com</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0507-1416-9683</t>
+          <t>0507-1472-6302</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 중앙대로1719번길 47 2층</t>
+          <t>부산광역시 금정구 금샘로485번길 65 B동 223호</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lsh20220</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8101,17 +8101,17 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>129</v>
+        <v>3</v>
       </c>
       <c r="R82" t="n">
-        <v>336</v>
+        <v>3</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -8120,17 +8120,17 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>2024917216</t>
+          <t>1993180780</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024917216</t>
+          <t>https://m.place.naver.com/place/1993180780</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8142,34 +8142,34 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>마이너짐</t>
+          <t>바디퀄리티</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>minorgym@naver.com</t>
+          <t>zoosoo4@naver.com</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0507-1361-9832</t>
+          <t>0507-1375-2643</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 금샘로 419 2층</t>
+          <t>부산광역시 금정구 중앙대로 1632 . 3층</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/minorgym</t>
+          <t>http://pf.kakao.com/_lxnxhaxj</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -8190,7 +8190,7 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8199,13 +8199,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>63</v>
+        <v>204</v>
       </c>
       <c r="Q83" t="n">
-        <v>196</v>
+        <v>65</v>
       </c>
       <c r="R83" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -8214,17 +8214,17 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>1003430536</t>
+          <t>1346534434</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1003430536</t>
+          <t>https://m.place.naver.com/place/1346534434</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8236,29 +8236,29 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>위드피트니스 &amp; PT 부산대점</t>
+          <t>더매력짐&amp;기구필라테스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>withfitness@naver.com</t>
+          <t>tmrgym1716@naver.com</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0507-1397-4887</t>
+          <t>0507-1419-6678</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 부산대학로 10 대우아파트 상가 위드피트니스 헬스장</t>
+          <t>부산광역시 금정구 부곡로 50</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/withfitness</t>
+          <t>https://blog.naver.com/tmrgym1716</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -8293,13 +8293,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1164</v>
+        <v>189</v>
       </c>
       <c r="Q84" t="n">
-        <v>1687</v>
+        <v>556</v>
       </c>
       <c r="R84" t="n">
-        <v>2851</v>
+        <v>745</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -8308,17 +8308,17 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>13415160</t>
+          <t>1639193921</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/13415160</t>
+          <t>https://m.place.naver.com/place/1639193921</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -8330,44 +8330,44 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>모션업PT 온천장점</t>
+          <t>마이너짐</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>rehab_coach@naver.com</t>
+          <t>minorgym@naver.com</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0507-1488-3306</t>
+          <t>0507-1361-9832</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>부산광역시 금정구 온천장로 136-1 6층 모션업PT</t>
+          <t>부산광역시 금정구 금샘로 419 2층</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://booking.naver.com/booking/6/bizes/765659</t>
+          <t>https://www.instagram.com/minorgym</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8387,13 +8387,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>160</v>
+        <v>63</v>
       </c>
       <c r="Q85" t="n">
-        <v>471</v>
+        <v>197</v>
       </c>
       <c r="R85" t="n">
-        <v>631</v>
+        <v>260</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -8402,17 +8402,17 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>1670613112</t>
+          <t>1003430536</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1670613112</t>
+          <t>https://m.place.naver.com/place/1003430536</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
